--- a/EKG_Kalite_Yönetim_Sistemi/00_Yönetim Sistemi Çerçevesi/01_Kapsam, Süreçler ve Görevler/EKG-YNT-MTR-04_ic_ve_dis_iletisim_musteri_temasi_ve_bildirim_yetkileri.xlsx
+++ b/EKG_Kalite_Yönetim_Sistemi/00_Yönetim Sistemi Çerçevesi/01_Kapsam, Süreçler ve Görevler/EKG-YNT-MTR-04_ic_ve_dis_iletisim_musteri_temasi_ve_bildirim_yetkileri.xlsx
@@ -914,7 +914,8 @@
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:headerFooter differentOddEven="0" differentFirst="0" scaleWithDoc="0" alignWithMargins="1">
     <x:oddHeader>&amp;L&amp;"Arial,Bold"&amp;11EKG-YNT-MTR-04&amp;C&amp;"Arial,Regular"&amp;11İç ve Dış İletişim, Müşteri Teması ve Bildirim Yetkileri Matrisi</x:oddHeader>
-    <x:oddFooter>&amp;L&amp;"Arial,Regular"&amp;11İlk Yayın: 04.05.2026 | Revizyon: 19.10.2026&amp;R&amp;11Sayfa &amp;P / &amp;N</x:oddFooter>
+    <x:oddFooter>&amp;L&amp;"Arial,Regular"&amp;11İlk Yayın: 01.06.2026 | Revizyon: 31.08.2026
+Revizyon nedeni: Doküman kimliği ve ana liste ile tarih eşleşmesi güncellendi.&amp;R&amp;11Sayfa &amp;P / &amp;N</x:oddFooter>
   </x:headerFooter>
   <x:drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rfb56d45757ae4a56"/>
   <x:tableParts count="1">
@@ -1176,7 +1177,8 @@
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:headerFooter differentOddEven="0" differentFirst="0" scaleWithDoc="0" alignWithMargins="1">
     <x:oddHeader>&amp;L&amp;"Arial,Bold"&amp;11EKG-YNT-MTR-04&amp;C&amp;"Arial,Regular"&amp;11İç ve Dış İletişim, Müşteri Teması ve Bildirim Yetkileri Matrisi</x:oddHeader>
-    <x:oddFooter>&amp;L&amp;"Arial,Regular"&amp;11İlk Yayın: 04.05.2026 | Revizyon: 19.10.2026&amp;R&amp;11Sayfa &amp;P / &amp;N</x:oddFooter>
+    <x:oddFooter>&amp;L&amp;"Arial,Regular"&amp;11İlk Yayın: 01.06.2026 | Revizyon: 31.08.2026
+Revizyon nedeni: Doküman kimliği ve ana liste ile tarih eşleşmesi güncellendi.&amp;R&amp;11Sayfa &amp;P / &amp;N</x:oddFooter>
   </x:headerFooter>
   <x:drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Re8e5bbf65ece4c62"/>
   <x:tableParts count="1">
@@ -1443,7 +1445,8 @@
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:headerFooter differentOddEven="0" differentFirst="0" scaleWithDoc="0" alignWithMargins="1">
     <x:oddHeader>&amp;L&amp;"Arial,Bold"&amp;11EKG-YNT-MTR-04&amp;C&amp;"Arial,Regular"&amp;11İç ve Dış İletişim, Müşteri Teması ve Bildirim Yetkileri Matrisi</x:oddHeader>
-    <x:oddFooter>&amp;L&amp;"Arial,Regular"&amp;11İlk Yayın: 04.05.2026 | Revizyon: 19.10.2026&amp;R&amp;11Sayfa &amp;P / &amp;N</x:oddFooter>
+    <x:oddFooter>&amp;L&amp;"Arial,Regular"&amp;11İlk Yayın: 01.06.2026 | Revizyon: 31.08.2026
+Revizyon nedeni: Doküman kimliği ve ana liste ile tarih eşleşmesi güncellendi.&amp;R&amp;11Sayfa &amp;P / &amp;N</x:oddFooter>
   </x:headerFooter>
   <x:drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R00f12d2d9af84656"/>
   <x:tableParts count="1">
